--- a/data/preliminaries/stellar/female/17-preliminary-r04-stellar-female.xlsx
+++ b/data/preliminaries/stellar/female/17-preliminary-r04-stellar-female.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛事数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第四轮" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'赛事数据'!$A$1:$I$57</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,60 +415,49 @@
   </sheetPr>
   <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>组别</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>组内排名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>全局排名</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>头像</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>得票数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -486,11 +469,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -512,8 +499,10 @@
           <t>赤尾光</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>894</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -527,11 +516,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -553,8 +546,10 @@
           <t>市之濑加那</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>618</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -568,11 +563,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>22</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -594,12 +593,14 @@
           <t>竹达彩奈</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>529</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -609,11 +610,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -631,12 +636,14 @@
           <t>佐佐木李子</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>520</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -646,11 +653,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>27</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -672,12 +683,14 @@
           <t>安济知佳</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>493</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -687,11 +700,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>29</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -709,12 +726,14 @@
           <t>上坂堇</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>476</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -724,11 +743,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>33</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -746,12 +769,14 @@
           <t>茅野爱衣</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>435</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -761,11 +786,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>34</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -787,12 +816,14 @@
           <t>户松遥</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>424</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -802,11 +833,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>39</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -828,8 +863,10 @@
           <t>种崎敦美</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>349</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -843,11 +880,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="n">
-        <v>42</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -865,8 +906,10 @@
           <t>茅野爱衣</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>307</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -880,11 +923,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>43</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -902,8 +949,10 @@
           <t>田村由香里</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>295</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -917,11 +966,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
-        <v>46</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -939,8 +992,10 @@
           <t>高桥伸也</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>280</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -954,11 +1009,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>47</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -976,8 +1035,10 @@
           <t>羊宫妃那</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>273</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -991,11 +1052,15 @@
           <t>女子5组</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="n">
-        <v>52</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1013,8 +1078,10 @@
           <t>早见沙织</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>152</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1028,11 +1095,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1054,8 +1125,10 @@
           <t>竹达彩奈</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>836</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1069,11 +1142,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>6</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1095,8 +1172,10 @@
           <t>上白石萌音</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>809</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1110,11 +1189,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1136,12 +1219,14 @@
           <t>洲崎绫</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>687</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1236,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>13</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1177,12 +1266,14 @@
           <t>小原好美</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>624</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1192,11 +1283,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>14</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1218,12 +1313,14 @@
           <t>羊宫妃那</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>622</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1233,11 +1330,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>17</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1259,12 +1360,14 @@
           <t>平野绫</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>591</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1274,11 +1377,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1300,12 +1407,14 @@
           <t>藤田茜</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>554</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1315,11 +1424,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" t="n">
-        <v>23</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1341,12 +1454,14 @@
           <t>斋藤千和</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>529</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1356,11 +1471,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>9</v>
-      </c>
-      <c r="C24" t="n">
-        <v>25</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1382,8 +1501,10 @@
           <t>户松遥</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>516</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1397,11 +1518,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>10</v>
-      </c>
-      <c r="C25" t="n">
-        <v>31</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1423,8 +1548,10 @@
           <t>鬼头明里</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>465</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1438,11 +1565,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C26" t="n">
-        <v>35</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1464,8 +1595,10 @@
           <t>长谷川育美</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>414</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1479,11 +1612,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>12</v>
-      </c>
-      <c r="C27" t="n">
-        <v>36</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1505,8 +1642,10 @@
           <t>桑原由气</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>406</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1520,11 +1659,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" t="n">
-        <v>53</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1542,8 +1685,10 @@
           <t>高桥李依</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>122</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1557,11 +1702,15 @@
           <t>女子6组</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>14</v>
-      </c>
-      <c r="C29" t="n">
-        <v>56</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1579,8 +1728,10 @@
           <t>白石晴香</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>43</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1594,11 +1745,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1620,8 +1775,10 @@
           <t>佐仓绫音</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>1089</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1635,11 +1792,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1661,8 +1822,10 @@
           <t>竹达彩奈</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>674</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1676,11 +1839,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="n">
-        <v>11</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1702,12 +1869,14 @@
           <t>水濑祈</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>656</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1717,11 +1886,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>18</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1743,12 +1916,14 @@
           <t>高桥李依</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>574</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1933,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>21</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1784,12 +1963,14 @@
           <t>加隈亚衣</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>549</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1799,11 +1980,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>26</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1825,12 +2010,14 @@
           <t>雨宫天</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>506</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1840,11 +2027,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" t="n">
-        <v>28</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1866,12 +2057,14 @@
           <t>早见沙织</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>486</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1881,11 +2074,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>8</v>
-      </c>
-      <c r="C37" t="n">
-        <v>30</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1907,12 +2104,14 @@
           <t>种田梨沙</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>466</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1922,11 +2121,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>32</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1940,8 +2143,10 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
-        <v>448</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1955,11 +2160,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>10</v>
-      </c>
-      <c r="C39" t="n">
-        <v>38</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1977,8 +2186,10 @@
           <t>东山奈央</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>350</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1992,11 +2203,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>11</v>
-      </c>
-      <c r="C40" t="n">
-        <v>41</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2014,8 +2229,10 @@
           <t>反田叶月</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>311</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2029,11 +2246,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C41" t="n">
-        <v>49</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2047,8 +2268,10 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
-        <v>224</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2062,11 +2285,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>13</v>
-      </c>
-      <c r="C42" t="n">
-        <v>51</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2084,8 +2311,10 @@
           <t>小林沙苗</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>167</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2099,11 +2328,15 @@
           <t>女子7组</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" t="n">
-        <v>54</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2121,8 +2354,10 @@
           <t>濑户麻沙美</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>65</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2136,11 +2371,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2162,8 +2401,10 @@
           <t>日笠阳子</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>926</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2177,11 +2418,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="n">
-        <v>5</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2203,8 +2448,10 @@
           <t>石见舞菜香</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>821</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2218,11 +2465,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>7</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2244,12 +2495,14 @@
           <t>寿美菜子</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>697</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2259,11 +2512,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="n">
-        <v>9</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2285,12 +2542,14 @@
           <t>米泽圆</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>679</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2300,11 +2559,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>12</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2326,12 +2589,14 @@
           <t>田口宏子</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>639</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2341,11 +2606,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="n">
-        <v>16</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2367,12 +2636,14 @@
           <t>种崎敦美</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>606</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2653,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>7</v>
-      </c>
-      <c r="C50" t="n">
-        <v>19</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2404,12 +2679,14 @@
           <t>理名</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>563</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2419,11 +2696,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="n">
-        <v>37</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2437,12 +2718,14 @@
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>403</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>晋级</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2452,11 +2735,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>40</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2474,8 +2761,10 @@
           <t>楠木灯</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>314</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2489,11 +2778,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>10</v>
-      </c>
-      <c r="C53" t="n">
-        <v>44</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2507,8 +2800,10 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>293</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2522,11 +2817,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>11</v>
-      </c>
-      <c r="C54" t="n">
-        <v>45</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2544,8 +2843,10 @@
           <t>若山诗音</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>290</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2559,11 +2860,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>12</v>
-      </c>
-      <c r="C55" t="n">
-        <v>48</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2581,8 +2886,10 @@
           <t>长谷川育美</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>259</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2596,11 +2903,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>13</v>
-      </c>
-      <c r="C56" t="n">
-        <v>50</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2618,8 +2929,10 @@
           <t>水树奈奈</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>212</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2633,11 +2946,15 @@
           <t>女子8组</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>14</v>
-      </c>
-      <c r="C57" t="n">
-        <v>55</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2655,8 +2972,10 @@
           <t>永濑安奈</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>62</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2665,7 +2984,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>